--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>51150.89</v>
+        <v>51905.57</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5144-1-CM26</t>
+          <t>5144-3-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio del Bienestar Gobierno Regional Coquimbo</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,6 +569,67 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>38973.68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5144-1-CM26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>75.943.840-K</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Servicio del Bienestar Gobierno Regional Coquimbo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>51905.57</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio del Bienestar Gobierno Regional Coquimbo</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
